--- a/metadata_capture/excel_utils/templates/worklist_template_blank.xlsx
+++ b/metadata_capture/excel_utils/templates/worklist_template_blank.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabewilson/Desktop/worklist_generation/metadata_capture/excel_utils/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A72D6CD0-5A72-4348-BCFC-D23BAE4E7F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B391299-E36D-6842-B1E9-775CC73A8172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="14680" yWindow="680" windowWidth="14720" windowHeight="16920" xr2:uid="{12DA0CF9-A1F3-4B47-B73A-18ED55D7EBC7}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{12DA0CF9-A1F3-4B47-B73A-18ED55D7EBC7}"/>
   </bookViews>
   <sheets>
     <sheet name="User" sheetId="1" r:id="rId1"/>
@@ -499,7 +500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
@@ -577,6 +578,42 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -588,51 +625,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -971,7 +963,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A45856-9C0F-D140-AD60-2AFFFFA45290}">
-  <dimension ref="A1:AV83"/>
+  <dimension ref="A1:AV76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
@@ -1015,7 +1007,6 @@
       <c r="AH1" t="s">
         <v>46</v>
       </c>
-      <c r="AI1" s="48"/>
       <c r="AM1" s="26"/>
       <c r="AO1" s="25"/>
     </row>
@@ -1029,16 +1020,12 @@
       </c>
       <c r="AE2" s="7"/>
       <c r="AF2" s="6"/>
-      <c r="AG2" s="43"/>
+      <c r="AG2" s="38"/>
       <c r="AH2" s="9"/>
-      <c r="AI2" s="49"/>
+      <c r="AI2" s="20"/>
       <c r="AJ2" s="28"/>
-      <c r="AK2" s="49"/>
-      <c r="AL2" s="48"/>
-      <c r="AM2" s="48"/>
-      <c r="AN2" s="48"/>
-      <c r="AO2" s="53"/>
-      <c r="AP2" s="48"/>
+      <c r="AK2" s="20"/>
+      <c r="AO2" s="25"/>
     </row>
     <row r="3" spans="1:48" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1050,16 +1037,12 @@
       </c>
       <c r="AE3" s="7"/>
       <c r="AF3" s="6"/>
-      <c r="AG3" s="43"/>
+      <c r="AG3" s="38"/>
       <c r="AH3" s="9"/>
-      <c r="AI3" s="49"/>
+      <c r="AI3" s="20"/>
       <c r="AJ3" s="28"/>
-      <c r="AK3" s="49"/>
-      <c r="AL3" s="48"/>
-      <c r="AM3" s="48"/>
-      <c r="AN3" s="48"/>
-      <c r="AO3" s="53"/>
-      <c r="AP3" s="48"/>
+      <c r="AK3" s="20"/>
+      <c r="AO3" s="25"/>
       <c r="AU3" s="42" t="s">
         <v>30</v>
       </c>
@@ -1098,20 +1081,17 @@
       </c>
       <c r="AE4" s="7"/>
       <c r="AF4" s="6"/>
-      <c r="AG4" s="43"/>
+      <c r="AG4" s="38"/>
       <c r="AH4" s="9"/>
-      <c r="AI4" s="50" t="s">
+      <c r="AI4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="AJ4" s="2"/>
-      <c r="AK4" s="54" t="s">
+      <c r="AK4" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="AL4" s="55"/>
-      <c r="AM4" s="48"/>
-      <c r="AN4" s="48"/>
-      <c r="AO4" s="53"/>
-      <c r="AP4" s="48"/>
+      <c r="AL4" s="48"/>
+      <c r="AO4" s="25"/>
       <c r="AU4" s="42"/>
       <c r="AV4" s="42"/>
     </row>
@@ -1202,20 +1182,17 @@
       </c>
       <c r="AE5" s="7"/>
       <c r="AF5" s="6"/>
-      <c r="AG5" s="43"/>
+      <c r="AG5" s="38"/>
       <c r="AH5" s="9"/>
-      <c r="AI5" s="50" t="s">
+      <c r="AI5" s="1" t="s">
         <v>53</v>
       </c>
       <c r="AJ5" s="2"/>
-      <c r="AK5" s="54" t="s">
+      <c r="AK5" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="AL5" s="55"/>
-      <c r="AM5" s="48"/>
-      <c r="AN5" s="48"/>
-      <c r="AO5" s="53"/>
-      <c r="AP5" s="48"/>
+      <c r="AL5" s="48"/>
+      <c r="AO5" s="25"/>
       <c r="AU5" s="42"/>
       <c r="AV5" s="42"/>
     </row>
@@ -1256,15 +1233,10 @@
       </c>
       <c r="AE6" s="7"/>
       <c r="AF6" s="6"/>
-      <c r="AG6" s="43"/>
+      <c r="AG6" s="38"/>
       <c r="AH6" s="9"/>
-      <c r="AI6" s="48"/>
-      <c r="AK6" s="49"/>
-      <c r="AL6" s="48"/>
-      <c r="AM6" s="48"/>
-      <c r="AN6" s="48"/>
-      <c r="AO6" s="53"/>
-      <c r="AP6" s="48"/>
+      <c r="AK6" s="20"/>
+      <c r="AO6" s="25"/>
       <c r="AU6" s="42"/>
       <c r="AV6" s="42"/>
     </row>
@@ -1301,15 +1273,9 @@
       </c>
       <c r="AE7" s="7"/>
       <c r="AF7" s="6"/>
-      <c r="AG7" s="43"/>
+      <c r="AG7" s="38"/>
       <c r="AH7" s="9"/>
-      <c r="AI7" s="48"/>
-      <c r="AK7" s="48"/>
-      <c r="AL7" s="48"/>
-      <c r="AM7" s="48"/>
-      <c r="AN7" s="48"/>
-      <c r="AO7" s="53"/>
-      <c r="AP7" s="48"/>
+      <c r="AO7" s="25"/>
       <c r="AU7" s="42"/>
       <c r="AV7" s="42"/>
     </row>
@@ -1346,22 +1312,19 @@
       </c>
       <c r="AE8" s="7"/>
       <c r="AF8" s="6"/>
-      <c r="AG8" s="43"/>
+      <c r="AG8" s="38"/>
       <c r="AH8" s="9"/>
-      <c r="AI8" s="50" t="s">
+      <c r="AI8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AJ8" s="45" t="s">
+      <c r="AJ8" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="AK8" s="54" t="s">
+      <c r="AK8" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="AL8" s="55"/>
-      <c r="AM8" s="48"/>
-      <c r="AN8" s="48"/>
-      <c r="AO8" s="53"/>
-      <c r="AP8" s="48"/>
+      <c r="AL8" s="48"/>
+      <c r="AO8" s="25"/>
       <c r="AU8" s="42"/>
       <c r="AV8" s="42"/>
     </row>
@@ -1401,18 +1364,15 @@
       </c>
       <c r="AE9" s="7"/>
       <c r="AF9" s="6"/>
-      <c r="AG9" s="43"/>
+      <c r="AG9" s="38"/>
       <c r="AH9" s="9"/>
-      <c r="AI9" s="50" t="s">
+      <c r="AI9" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AJ9" s="2"/>
-      <c r="AK9" s="54"/>
-      <c r="AL9" s="55"/>
-      <c r="AM9" s="48"/>
-      <c r="AN9" s="48"/>
-      <c r="AO9" s="53"/>
-      <c r="AP9" s="48"/>
+      <c r="AK9" s="47"/>
+      <c r="AL9" s="48"/>
+      <c r="AO9" s="25"/>
       <c r="AU9" s="42"/>
       <c r="AV9" s="42"/>
     </row>
@@ -1453,20 +1413,17 @@
       </c>
       <c r="AE10" s="7"/>
       <c r="AF10" s="6"/>
-      <c r="AG10" s="43"/>
+      <c r="AG10" s="38"/>
       <c r="AH10" s="9"/>
-      <c r="AI10" s="51" t="s">
+      <c r="AI10" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="AJ10" s="46" t="s">
+      <c r="AJ10" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="AK10" s="54"/>
-      <c r="AL10" s="55"/>
-      <c r="AM10" s="48"/>
-      <c r="AN10" s="48"/>
-      <c r="AO10" s="53"/>
-      <c r="AP10" s="48"/>
+      <c r="AK10" s="47"/>
+      <c r="AL10" s="48"/>
+      <c r="AO10" s="25"/>
       <c r="AU10" s="42"/>
       <c r="AV10" s="42"/>
     </row>
@@ -1507,16 +1464,13 @@
       </c>
       <c r="AE11" s="7"/>
       <c r="AF11" s="6"/>
-      <c r="AG11" s="43"/>
+      <c r="AG11" s="38"/>
       <c r="AH11" s="9"/>
-      <c r="AI11" s="52"/>
-      <c r="AJ11" s="47"/>
-      <c r="AK11" s="56"/>
-      <c r="AL11" s="56"/>
-      <c r="AM11" s="48"/>
-      <c r="AN11" s="48"/>
-      <c r="AO11" s="53"/>
-      <c r="AP11" s="48"/>
+      <c r="AI11" s="44"/>
+      <c r="AJ11" s="46"/>
+      <c r="AK11" s="27"/>
+      <c r="AL11" s="27"/>
+      <c r="AO11" s="25"/>
       <c r="AU11" s="42"/>
       <c r="AV11" s="42"/>
     </row>
@@ -1557,16 +1511,12 @@
       </c>
       <c r="AE12" s="7"/>
       <c r="AF12" s="6"/>
-      <c r="AG12" s="43"/>
+      <c r="AG12" s="38"/>
       <c r="AH12" s="9"/>
-      <c r="AI12" s="49"/>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="49"/>
-      <c r="AL12" s="48"/>
-      <c r="AM12" s="48"/>
-      <c r="AN12" s="48"/>
-      <c r="AO12" s="53"/>
-      <c r="AP12" s="48"/>
+      <c r="AI12" s="20"/>
+      <c r="AJ12" s="20"/>
+      <c r="AK12" s="20"/>
+      <c r="AO12" s="25"/>
       <c r="AU12" s="42"/>
       <c r="AV12" s="42"/>
     </row>
@@ -1607,16 +1557,12 @@
       </c>
       <c r="AE13" s="7"/>
       <c r="AF13" s="6"/>
-      <c r="AG13" s="43"/>
+      <c r="AG13" s="38"/>
       <c r="AH13" s="9"/>
-      <c r="AI13" s="49"/>
-      <c r="AJ13" s="49"/>
-      <c r="AK13" s="49"/>
-      <c r="AL13" s="48"/>
-      <c r="AM13" s="48"/>
-      <c r="AN13" s="48"/>
-      <c r="AO13" s="53"/>
-      <c r="AP13" s="48"/>
+      <c r="AI13" s="20"/>
+      <c r="AJ13" s="20"/>
+      <c r="AK13" s="20"/>
+      <c r="AO13" s="25"/>
       <c r="AU13" s="42"/>
       <c r="AV13" s="42"/>
     </row>
@@ -1657,16 +1603,9 @@
       </c>
       <c r="AE14" s="7"/>
       <c r="AF14" s="6"/>
-      <c r="AG14" s="43"/>
+      <c r="AG14" s="38"/>
       <c r="AH14" s="9"/>
-      <c r="AI14" s="48"/>
-      <c r="AJ14" s="48"/>
-      <c r="AK14" s="48"/>
-      <c r="AL14" s="48"/>
-      <c r="AM14" s="48"/>
-      <c r="AN14" s="48"/>
-      <c r="AO14" s="53"/>
-      <c r="AP14" s="48"/>
+      <c r="AO14" s="25"/>
       <c r="AU14" s="42"/>
       <c r="AV14" s="42"/>
     </row>
@@ -1703,16 +1642,9 @@
       </c>
       <c r="AE15" s="7"/>
       <c r="AF15" s="6"/>
-      <c r="AG15" s="43"/>
+      <c r="AG15" s="38"/>
       <c r="AH15" s="9"/>
-      <c r="AI15" s="48"/>
-      <c r="AJ15" s="48"/>
-      <c r="AK15" s="48"/>
-      <c r="AL15" s="48"/>
-      <c r="AM15" s="48"/>
-      <c r="AN15" s="48"/>
-      <c r="AO15" s="53"/>
-      <c r="AP15" s="48"/>
+      <c r="AO15" s="25"/>
     </row>
     <row r="16" spans="1:48" x14ac:dyDescent="0.2">
       <c r="D16" t="s">
@@ -1747,18 +1679,11 @@
       </c>
       <c r="AE16" s="7"/>
       <c r="AF16" s="6"/>
-      <c r="AG16" s="43"/>
+      <c r="AG16" s="38"/>
       <c r="AH16" s="9"/>
-      <c r="AI16" s="48"/>
-      <c r="AJ16" s="48"/>
-      <c r="AK16" s="48"/>
-      <c r="AL16" s="48"/>
-      <c r="AM16" s="48"/>
-      <c r="AN16" s="48"/>
-      <c r="AO16" s="53"/>
-      <c r="AP16" s="48"/>
-    </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AO16" s="25"/>
+    </row>
+    <row r="17" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D17" t="s">
         <v>24</v>
       </c>
@@ -1791,18 +1716,11 @@
       </c>
       <c r="AE17" s="7"/>
       <c r="AF17" s="6"/>
-      <c r="AG17" s="43"/>
+      <c r="AG17" s="38"/>
       <c r="AH17" s="9"/>
-      <c r="AI17" s="48"/>
-      <c r="AJ17" s="48"/>
-      <c r="AK17" s="48"/>
-      <c r="AL17" s="48"/>
-      <c r="AM17" s="48"/>
-      <c r="AN17" s="48"/>
-      <c r="AO17" s="53"/>
-      <c r="AP17" s="48"/>
-    </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AO17" s="25"/>
+    </row>
+    <row r="18" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D18" t="s">
         <v>25</v>
       </c>
@@ -1835,18 +1753,14 @@
       </c>
       <c r="AE18" s="7"/>
       <c r="AF18" s="6"/>
-      <c r="AG18" s="43"/>
+      <c r="AG18" s="38"/>
       <c r="AH18" s="9"/>
-      <c r="AI18" s="49"/>
-      <c r="AJ18" s="49"/>
-      <c r="AK18" s="49"/>
-      <c r="AL18" s="48"/>
-      <c r="AM18" s="48"/>
-      <c r="AN18" s="48"/>
-      <c r="AO18" s="53"/>
-      <c r="AP18" s="48"/>
-    </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AI18" s="20"/>
+      <c r="AJ18" s="20"/>
+      <c r="AK18" s="20"/>
+      <c r="AO18" s="25"/>
+    </row>
+    <row r="19" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D19" t="s">
         <v>26</v>
       </c>
@@ -1879,18 +1793,14 @@
       </c>
       <c r="AE19" s="7"/>
       <c r="AF19" s="6"/>
-      <c r="AG19" s="43"/>
+      <c r="AG19" s="38"/>
       <c r="AH19" s="9"/>
-      <c r="AI19" s="49"/>
-      <c r="AJ19" s="49"/>
-      <c r="AK19" s="49"/>
-      <c r="AL19" s="48"/>
-      <c r="AM19" s="48"/>
-      <c r="AN19" s="48"/>
-      <c r="AO19" s="53"/>
-      <c r="AP19" s="48"/>
-    </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AI19" s="20"/>
+      <c r="AJ19" s="20"/>
+      <c r="AK19" s="20"/>
+      <c r="AO19" s="25"/>
+    </row>
+    <row r="20" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D20" t="s">
         <v>27</v>
       </c>
@@ -1923,18 +1833,14 @@
       </c>
       <c r="AE20" s="7"/>
       <c r="AF20" s="6"/>
-      <c r="AG20" s="43"/>
+      <c r="AG20" s="38"/>
       <c r="AH20" s="9"/>
-      <c r="AI20" s="49"/>
-      <c r="AJ20" s="49"/>
-      <c r="AK20" s="49"/>
-      <c r="AL20" s="48"/>
-      <c r="AM20" s="48"/>
-      <c r="AN20" s="48"/>
-      <c r="AO20" s="53"/>
-      <c r="AP20" s="48"/>
-    </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AI20" s="20"/>
+      <c r="AJ20" s="20"/>
+      <c r="AK20" s="20"/>
+      <c r="AO20" s="25"/>
+    </row>
+    <row r="21" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D21" t="s">
         <v>28</v>
       </c>
@@ -1967,18 +1873,14 @@
       </c>
       <c r="AE21" s="7"/>
       <c r="AF21" s="6"/>
-      <c r="AG21" s="43"/>
+      <c r="AG21" s="38"/>
       <c r="AH21" s="9"/>
-      <c r="AI21" s="49"/>
-      <c r="AJ21" s="49"/>
-      <c r="AK21" s="49"/>
-      <c r="AL21" s="48"/>
-      <c r="AM21" s="48"/>
-      <c r="AN21" s="48"/>
-      <c r="AO21" s="53"/>
-      <c r="AP21" s="48"/>
-    </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AI21" s="20"/>
+      <c r="AJ21" s="20"/>
+      <c r="AK21" s="20"/>
+      <c r="AO21" s="25"/>
+    </row>
+    <row r="22" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="D22" s="3"/>
@@ -2011,18 +1913,14 @@
       </c>
       <c r="AE22" s="7"/>
       <c r="AF22" s="6"/>
-      <c r="AG22" s="43"/>
+      <c r="AG22" s="38"/>
       <c r="AH22" s="9"/>
-      <c r="AI22" s="49"/>
-      <c r="AJ22" s="49"/>
-      <c r="AK22" s="49"/>
-      <c r="AL22" s="48"/>
-      <c r="AM22" s="48"/>
-      <c r="AN22" s="48"/>
-      <c r="AO22" s="53"/>
-      <c r="AP22" s="48"/>
-    </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AI22" s="20"/>
+      <c r="AJ22" s="20"/>
+      <c r="AK22" s="20"/>
+      <c r="AO22" s="25"/>
+    </row>
+    <row r="23" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>10</v>
       </c>
@@ -2109,18 +2007,14 @@
       </c>
       <c r="AE23" s="7"/>
       <c r="AF23" s="6"/>
-      <c r="AG23" s="43"/>
+      <c r="AG23" s="38"/>
       <c r="AH23" s="9"/>
-      <c r="AI23" s="49"/>
-      <c r="AJ23" s="49"/>
-      <c r="AK23" s="49"/>
-      <c r="AL23" s="48"/>
-      <c r="AM23" s="48"/>
-      <c r="AN23" s="48"/>
-      <c r="AO23" s="53"/>
-      <c r="AP23" s="48"/>
-    </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AI23" s="20"/>
+      <c r="AJ23" s="20"/>
+      <c r="AK23" s="20"/>
+      <c r="AO23" s="25"/>
+    </row>
+    <row r="24" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A24" s="35" t="s">
         <v>19</v>
       </c>
@@ -2157,18 +2051,14 @@
       </c>
       <c r="AE24" s="7"/>
       <c r="AF24" s="6"/>
-      <c r="AG24" s="43"/>
+      <c r="AG24" s="38"/>
       <c r="AH24" s="9"/>
-      <c r="AI24" s="49"/>
-      <c r="AJ24" s="49"/>
-      <c r="AK24" s="49"/>
-      <c r="AL24" s="48"/>
-      <c r="AM24" s="48"/>
-      <c r="AN24" s="48"/>
-      <c r="AO24" s="53"/>
-      <c r="AP24" s="48"/>
-    </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AI24" s="20"/>
+      <c r="AJ24" s="20"/>
+      <c r="AK24" s="20"/>
+      <c r="AO24" s="25"/>
+    </row>
+    <row r="25" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D25" t="s">
         <v>14</v>
       </c>
@@ -2201,18 +2091,14 @@
       </c>
       <c r="AE25" s="7"/>
       <c r="AF25" s="6"/>
-      <c r="AG25" s="43"/>
+      <c r="AG25" s="38"/>
       <c r="AH25" s="9"/>
-      <c r="AI25" s="49"/>
-      <c r="AJ25" s="49"/>
-      <c r="AK25" s="49"/>
-      <c r="AL25" s="48"/>
-      <c r="AM25" s="48"/>
-      <c r="AN25" s="48"/>
-      <c r="AO25" s="53"/>
-      <c r="AP25" s="48"/>
-    </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AI25" s="20"/>
+      <c r="AJ25" s="20"/>
+      <c r="AK25" s="20"/>
+      <c r="AO25" s="25"/>
+    </row>
+    <row r="26" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D26" t="s">
         <v>15</v>
       </c>
@@ -2245,18 +2131,14 @@
       </c>
       <c r="AE26" s="7"/>
       <c r="AF26" s="6"/>
-      <c r="AG26" s="43"/>
+      <c r="AG26" s="38"/>
       <c r="AH26" s="9"/>
-      <c r="AI26" s="49"/>
-      <c r="AJ26" s="49"/>
-      <c r="AK26" s="49"/>
-      <c r="AL26" s="48"/>
-      <c r="AM26" s="48"/>
-      <c r="AN26" s="48"/>
-      <c r="AO26" s="53"/>
-      <c r="AP26" s="48"/>
-    </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AI26" s="20"/>
+      <c r="AJ26" s="20"/>
+      <c r="AK26" s="20"/>
+      <c r="AO26" s="25"/>
+    </row>
+    <row r="27" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B27" s="26" t="s">
         <v>64</v>
       </c>
@@ -2292,18 +2174,14 @@
       </c>
       <c r="AE27" s="7"/>
       <c r="AF27" s="6"/>
-      <c r="AG27" s="43"/>
+      <c r="AG27" s="38"/>
       <c r="AH27" s="9"/>
-      <c r="AI27" s="49"/>
-      <c r="AJ27" s="49"/>
-      <c r="AK27" s="49"/>
-      <c r="AL27" s="48"/>
-      <c r="AM27" s="48"/>
-      <c r="AN27" s="48"/>
-      <c r="AO27" s="53"/>
-      <c r="AP27" s="48"/>
-    </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AI27" s="20"/>
+      <c r="AJ27" s="20"/>
+      <c r="AK27" s="20"/>
+      <c r="AO27" s="25"/>
+    </row>
+    <row r="28" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>1</v>
       </c>
@@ -2340,18 +2218,14 @@
       </c>
       <c r="AE28" s="7"/>
       <c r="AF28" s="6"/>
-      <c r="AG28" s="43"/>
+      <c r="AG28" s="38"/>
       <c r="AH28" s="9"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
-      <c r="AL28" s="48"/>
-      <c r="AM28" s="48"/>
-      <c r="AN28" s="48"/>
-      <c r="AO28" s="53"/>
-      <c r="AP28" s="48"/>
-    </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AI28" s="20"/>
+      <c r="AJ28" s="20"/>
+      <c r="AK28" s="20"/>
+      <c r="AO28" s="25"/>
+    </row>
+    <row r="29" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>2</v>
       </c>
@@ -2388,18 +2262,14 @@
       </c>
       <c r="AE29" s="7"/>
       <c r="AF29" s="6"/>
-      <c r="AG29" s="43"/>
+      <c r="AG29" s="38"/>
       <c r="AH29" s="9"/>
-      <c r="AI29" s="49"/>
-      <c r="AJ29" s="49"/>
-      <c r="AK29" s="49"/>
-      <c r="AL29" s="48"/>
-      <c r="AM29" s="48"/>
-      <c r="AN29" s="48"/>
-      <c r="AO29" s="53"/>
-      <c r="AP29" s="48"/>
-    </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AI29" s="20"/>
+      <c r="AJ29" s="20"/>
+      <c r="AK29" s="20"/>
+      <c r="AO29" s="25"/>
+    </row>
+    <row r="30" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>3</v>
       </c>
@@ -2436,18 +2306,14 @@
       </c>
       <c r="AE30" s="7"/>
       <c r="AF30" s="6"/>
-      <c r="AG30" s="43"/>
+      <c r="AG30" s="38"/>
       <c r="AH30" s="9"/>
-      <c r="AI30" s="49"/>
-      <c r="AJ30" s="49"/>
-      <c r="AK30" s="49"/>
-      <c r="AL30" s="48"/>
-      <c r="AM30" s="48"/>
-      <c r="AN30" s="48"/>
-      <c r="AO30" s="53"/>
-      <c r="AP30" s="48"/>
-    </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AI30" s="20"/>
+      <c r="AJ30" s="20"/>
+      <c r="AK30" s="20"/>
+      <c r="AO30" s="25"/>
+    </row>
+    <row r="31" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>4</v>
       </c>
@@ -2484,18 +2350,14 @@
       </c>
       <c r="AE31" s="7"/>
       <c r="AF31" s="6"/>
-      <c r="AG31" s="43"/>
+      <c r="AG31" s="38"/>
       <c r="AH31" s="9"/>
-      <c r="AI31" s="49"/>
-      <c r="AJ31" s="49"/>
-      <c r="AK31" s="49"/>
-      <c r="AL31" s="48"/>
-      <c r="AM31" s="48"/>
-      <c r="AN31" s="48"/>
-      <c r="AO31" s="53"/>
-      <c r="AP31" s="48"/>
-    </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AI31" s="20"/>
+      <c r="AJ31" s="20"/>
+      <c r="AK31" s="20"/>
+      <c r="AO31" s="25"/>
+    </row>
+    <row r="32" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
@@ -2532,18 +2394,11 @@
       </c>
       <c r="AE32" s="7"/>
       <c r="AF32" s="6"/>
-      <c r="AG32" s="43"/>
+      <c r="AG32" s="38"/>
       <c r="AH32" s="9"/>
-      <c r="AI32" s="48"/>
-      <c r="AJ32" s="48"/>
-      <c r="AK32" s="48"/>
-      <c r="AL32" s="48"/>
-      <c r="AM32" s="48"/>
-      <c r="AN32" s="48"/>
-      <c r="AO32" s="53"/>
-      <c r="AP32" s="48"/>
-    </row>
-    <row r="33" spans="1:42" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AO32" s="25"/>
+    </row>
+    <row r="33" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D33" t="s">
         <v>22</v>
       </c>
@@ -2576,18 +2431,11 @@
       </c>
       <c r="AE33" s="7"/>
       <c r="AF33" s="6"/>
-      <c r="AG33" s="43"/>
+      <c r="AG33" s="38"/>
       <c r="AH33" s="9"/>
-      <c r="AI33" s="48"/>
-      <c r="AJ33" s="48"/>
-      <c r="AK33" s="48"/>
-      <c r="AL33" s="48"/>
-      <c r="AM33" s="48"/>
-      <c r="AN33" s="48"/>
-      <c r="AO33" s="53"/>
-      <c r="AP33" s="48"/>
-    </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AO33" s="25"/>
+    </row>
+    <row r="34" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D34" t="s">
         <v>23</v>
       </c>
@@ -2622,15 +2470,8 @@
       <c r="AF34" s="6"/>
       <c r="AG34" s="6"/>
       <c r="AH34" s="9"/>
-      <c r="AI34" s="48"/>
-      <c r="AK34" s="48"/>
-      <c r="AL34" s="48"/>
-      <c r="AM34" s="48"/>
-      <c r="AN34" s="48"/>
-      <c r="AO34" s="48"/>
-      <c r="AP34" s="48"/>
-    </row>
-    <row r="35" spans="1:42" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D35" t="s">
         <v>24</v>
       </c>
@@ -2665,15 +2506,8 @@
       <c r="AF35" s="6"/>
       <c r="AG35" s="6"/>
       <c r="AH35" s="9"/>
-      <c r="AI35" s="48"/>
-      <c r="AK35" s="48"/>
-      <c r="AL35" s="48"/>
-      <c r="AM35" s="48"/>
-      <c r="AN35" s="48"/>
-      <c r="AO35" s="48"/>
-      <c r="AP35" s="48"/>
-    </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D36" t="s">
         <v>25</v>
       </c>
@@ -2708,15 +2542,8 @@
       <c r="AF36" s="6"/>
       <c r="AG36" s="6"/>
       <c r="AH36" s="9"/>
-      <c r="AI36" s="48"/>
-      <c r="AK36" s="48"/>
-      <c r="AL36" s="48"/>
-      <c r="AM36" s="48"/>
-      <c r="AN36" s="48"/>
-      <c r="AO36" s="48"/>
-      <c r="AP36" s="48"/>
-    </row>
-    <row r="37" spans="1:42" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D37" t="s">
         <v>26</v>
       </c>
@@ -2751,15 +2578,8 @@
       <c r="AF37" s="6"/>
       <c r="AG37" s="6"/>
       <c r="AH37" s="9"/>
-      <c r="AI37" s="48"/>
-      <c r="AK37" s="48"/>
-      <c r="AL37" s="48"/>
-      <c r="AM37" s="48"/>
-      <c r="AN37" s="48"/>
-      <c r="AO37" s="48"/>
-      <c r="AP37" s="48"/>
-    </row>
-    <row r="38" spans="1:42" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D38" t="s">
         <v>27</v>
       </c>
@@ -2794,15 +2614,8 @@
       <c r="AF38" s="6"/>
       <c r="AG38" s="6"/>
       <c r="AH38" s="9"/>
-      <c r="AI38" s="48"/>
-      <c r="AK38" s="48"/>
-      <c r="AL38" s="48"/>
-      <c r="AM38" s="48"/>
-      <c r="AN38" s="48"/>
-      <c r="AO38" s="48"/>
-      <c r="AP38" s="48"/>
-    </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D39" t="s">
         <v>28</v>
       </c>
@@ -2837,15 +2650,8 @@
       <c r="AF39" s="6"/>
       <c r="AG39" s="6"/>
       <c r="AH39" s="9"/>
-      <c r="AI39" s="48"/>
-      <c r="AK39" s="48"/>
-      <c r="AL39" s="48"/>
-      <c r="AM39" s="48"/>
-      <c r="AN39" s="48"/>
-      <c r="AO39" s="48"/>
-      <c r="AP39" s="48"/>
-    </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="D40" s="3"/>
@@ -2880,16 +2686,10 @@
       <c r="AF40" s="6"/>
       <c r="AG40" s="6"/>
       <c r="AH40" s="9"/>
-      <c r="AI40" s="48"/>
       <c r="AJ40" s="27"/>
-      <c r="AK40" s="56"/>
-      <c r="AL40" s="48"/>
-      <c r="AM40" s="48"/>
-      <c r="AN40" s="48"/>
-      <c r="AO40" s="48"/>
-      <c r="AP40" s="48"/>
-    </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AK40" s="27"/>
+    </row>
+    <row r="41" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>10</v>
       </c>
@@ -2978,16 +2778,10 @@
       <c r="AF41" s="6"/>
       <c r="AG41" s="6"/>
       <c r="AH41" s="9"/>
-      <c r="AI41" s="48"/>
       <c r="AJ41" s="27"/>
-      <c r="AK41" s="56"/>
-      <c r="AL41" s="48"/>
-      <c r="AM41" s="48"/>
-      <c r="AN41" s="48"/>
-      <c r="AO41" s="48"/>
-      <c r="AP41" s="48"/>
-    </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AK41" s="27"/>
+    </row>
+    <row r="42" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A42" s="35" t="s">
         <v>14</v>
       </c>
@@ -3026,9 +2820,8 @@
       <c r="AF42" s="6"/>
       <c r="AG42" s="6"/>
       <c r="AH42" s="9"/>
-      <c r="AI42" s="48"/>
-    </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D43" t="s">
         <v>14</v>
       </c>
@@ -3063,9 +2856,8 @@
       <c r="AF43" s="6"/>
       <c r="AG43" s="6"/>
       <c r="AH43" s="9"/>
-      <c r="AI43" s="48"/>
-    </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D44" t="s">
         <v>15</v>
       </c>
@@ -3100,9 +2892,8 @@
       <c r="AF44" s="6"/>
       <c r="AG44" s="6"/>
       <c r="AH44" s="9"/>
-      <c r="AI44" s="48"/>
-    </row>
-    <row r="45" spans="1:42" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B45" s="26" t="s">
         <v>64</v>
       </c>
@@ -3140,9 +2931,8 @@
       <c r="AF45" s="6"/>
       <c r="AG45" s="6"/>
       <c r="AH45" s="9"/>
-      <c r="AI45" s="48"/>
-    </row>
-    <row r="46" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>1</v>
       </c>
@@ -3181,9 +2971,8 @@
       <c r="AF46" s="6"/>
       <c r="AG46" s="6"/>
       <c r="AH46" s="9"/>
-      <c r="AI46" s="48"/>
-    </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>2</v>
       </c>
@@ -3222,9 +3011,8 @@
       <c r="AF47" s="6"/>
       <c r="AG47" s="6"/>
       <c r="AH47" s="9"/>
-      <c r="AI47" s="48"/>
-    </row>
-    <row r="48" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>3</v>
       </c>
@@ -3260,10 +3048,9 @@
         <v>47</v>
       </c>
       <c r="AE48" s="7"/>
-      <c r="AF48" s="44"/>
+      <c r="AF48" s="39"/>
       <c r="AG48" s="6"/>
       <c r="AH48" s="9"/>
-      <c r="AI48" s="48"/>
     </row>
     <row r="49" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A49">
@@ -3301,10 +3088,9 @@
         <v>48</v>
       </c>
       <c r="AE49" s="7"/>
-      <c r="AF49" s="44"/>
+      <c r="AF49" s="39"/>
       <c r="AG49" s="6"/>
       <c r="AH49" s="9"/>
-      <c r="AI49" s="48"/>
     </row>
     <row r="50" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A50">
@@ -3342,10 +3128,9 @@
         <v>49</v>
       </c>
       <c r="AE50" s="7"/>
-      <c r="AF50" s="44"/>
+      <c r="AF50" s="39"/>
       <c r="AG50" s="6"/>
       <c r="AH50" s="9"/>
-      <c r="AI50" s="48"/>
     </row>
     <row r="51" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D51" t="s">
@@ -3382,7 +3167,6 @@
       <c r="AF51" s="12"/>
       <c r="AG51" s="12"/>
       <c r="AH51" s="9"/>
-      <c r="AI51" s="48"/>
     </row>
     <row r="52" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D52" t="s">
@@ -3412,7 +3196,6 @@
       <c r="Z52" s="9"/>
       <c r="AA52" s="9"/>
       <c r="AB52" s="8"/>
-      <c r="AI52" s="48"/>
     </row>
     <row r="53" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D53" t="s">
@@ -3444,7 +3227,6 @@
       <c r="AB53" s="8"/>
       <c r="AE53" s="20"/>
       <c r="AF53" s="20"/>
-      <c r="AI53" s="48"/>
       <c r="AM53" s="20"/>
       <c r="AN53" s="20"/>
     </row>
@@ -3478,7 +3260,6 @@
       <c r="AB54" s="8"/>
       <c r="AE54" s="20"/>
       <c r="AF54" s="20"/>
-      <c r="AI54" s="48"/>
       <c r="AM54" s="20"/>
       <c r="AN54" s="20"/>
     </row>
@@ -3510,14 +3291,8 @@
       <c r="Z55" s="9"/>
       <c r="AA55" s="9"/>
       <c r="AB55" s="8"/>
-      <c r="AD55" s="48"/>
-      <c r="AE55" s="49"/>
-      <c r="AF55" s="49"/>
-      <c r="AG55" s="48"/>
-      <c r="AH55" s="48"/>
-      <c r="AI55" s="48"/>
-      <c r="AJ55" s="48"/>
-      <c r="AK55" s="48"/>
+      <c r="AE55" s="20"/>
+      <c r="AF55" s="20"/>
       <c r="AM55" s="20"/>
       <c r="AN55" s="20"/>
     </row>
@@ -3549,14 +3324,6 @@
       <c r="Z56" s="9"/>
       <c r="AA56" s="9"/>
       <c r="AB56" s="8"/>
-      <c r="AD56" s="48"/>
-      <c r="AE56" s="48"/>
-      <c r="AF56" s="48"/>
-      <c r="AG56" s="48"/>
-      <c r="AH56" s="48"/>
-      <c r="AI56" s="48"/>
-      <c r="AJ56" s="48"/>
-      <c r="AK56" s="48"/>
     </row>
     <row r="57" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D57" t="s">
@@ -3586,14 +3353,7 @@
       <c r="Z57" s="17"/>
       <c r="AA57" s="17"/>
       <c r="AB57" s="18"/>
-      <c r="AD57" s="48"/>
-      <c r="AE57" s="48"/>
-      <c r="AF57" s="48"/>
-      <c r="AG57" s="48"/>
-      <c r="AH57" s="48"/>
-      <c r="AI57" s="48"/>
-      <c r="AJ57" s="48"/>
-      <c r="AK57" s="49"/>
+      <c r="AK57" s="20"/>
       <c r="AL57" s="21"/>
       <c r="AM57" s="20"/>
       <c r="AN57" s="20"/>
@@ -3626,14 +3386,7 @@
       <c r="Z58" s="3"/>
       <c r="AA58" s="3"/>
       <c r="AB58" s="3"/>
-      <c r="AD58" s="48"/>
-      <c r="AE58" s="48"/>
-      <c r="AF58" s="48"/>
-      <c r="AG58" s="48"/>
-      <c r="AH58" s="48"/>
-      <c r="AI58" s="48"/>
-      <c r="AJ58" s="48"/>
-      <c r="AK58" s="49"/>
+      <c r="AK58" s="20"/>
       <c r="AL58" s="21"/>
       <c r="AM58" s="20"/>
       <c r="AN58" s="20"/>
@@ -3720,14 +3473,7 @@
       <c r="AB59">
         <v>24</v>
       </c>
-      <c r="AD59" s="48"/>
-      <c r="AE59" s="48"/>
-      <c r="AF59" s="48"/>
-      <c r="AG59" s="48"/>
-      <c r="AH59" s="48"/>
-      <c r="AI59" s="48"/>
-      <c r="AJ59" s="48"/>
-      <c r="AK59" s="49"/>
+      <c r="AK59" s="20"/>
       <c r="AL59" s="21"/>
       <c r="AM59" s="20"/>
       <c r="AN59" s="20"/>
@@ -3764,14 +3510,6 @@
       <c r="Z60" s="14"/>
       <c r="AA60" s="14"/>
       <c r="AB60" s="15"/>
-      <c r="AD60" s="48"/>
-      <c r="AE60" s="48"/>
-      <c r="AF60" s="48"/>
-      <c r="AG60" s="48"/>
-      <c r="AH60" s="48"/>
-      <c r="AI60" s="48"/>
-      <c r="AJ60" s="48"/>
-      <c r="AK60" s="48"/>
     </row>
     <row r="61" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D61" t="s">
@@ -3801,14 +3539,6 @@
       <c r="Z61" s="9"/>
       <c r="AA61" s="9"/>
       <c r="AB61" s="8"/>
-      <c r="AD61" s="48"/>
-      <c r="AE61" s="48"/>
-      <c r="AF61" s="48"/>
-      <c r="AG61" s="48"/>
-      <c r="AH61" s="48"/>
-      <c r="AI61" s="48"/>
-      <c r="AJ61" s="48"/>
-      <c r="AK61" s="48"/>
     </row>
     <row r="62" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D62" t="s">
@@ -3838,14 +3568,6 @@
       <c r="Z62" s="9"/>
       <c r="AA62" s="9"/>
       <c r="AB62" s="8"/>
-      <c r="AD62" s="48"/>
-      <c r="AE62" s="48"/>
-      <c r="AF62" s="48"/>
-      <c r="AG62" s="48"/>
-      <c r="AH62" s="48"/>
-      <c r="AI62" s="48"/>
-      <c r="AJ62" s="48"/>
-      <c r="AK62" s="48"/>
     </row>
     <row r="63" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B63" s="26" t="s">
@@ -3878,14 +3600,6 @@
       <c r="Z63" s="9"/>
       <c r="AA63" s="9"/>
       <c r="AB63" s="8"/>
-      <c r="AD63" s="48"/>
-      <c r="AE63" s="48"/>
-      <c r="AF63" s="48"/>
-      <c r="AG63" s="48"/>
-      <c r="AH63" s="48"/>
-      <c r="AI63" s="48"/>
-      <c r="AJ63" s="48"/>
-      <c r="AK63" s="48"/>
     </row>
     <row r="64" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A64">
@@ -3919,16 +3633,8 @@
       <c r="Z64" s="9"/>
       <c r="AA64" s="9"/>
       <c r="AB64" s="8"/>
-      <c r="AD64" s="48"/>
-      <c r="AE64" s="48"/>
-      <c r="AF64" s="48"/>
-      <c r="AG64" s="48"/>
-      <c r="AH64" s="48"/>
-      <c r="AI64" s="48"/>
-      <c r="AJ64" s="48"/>
-      <c r="AK64" s="48"/>
-    </row>
-    <row r="65" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>2</v>
       </c>
@@ -3960,16 +3666,8 @@
       <c r="Z65" s="9"/>
       <c r="AA65" s="9"/>
       <c r="AB65" s="8"/>
-      <c r="AD65" s="48"/>
-      <c r="AE65" s="48"/>
-      <c r="AF65" s="48"/>
-      <c r="AG65" s="48"/>
-      <c r="AH65" s="48"/>
-      <c r="AI65" s="48"/>
-      <c r="AJ65" s="48"/>
-      <c r="AK65" s="48"/>
-    </row>
-    <row r="66" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>3</v>
       </c>
@@ -4001,16 +3699,8 @@
       <c r="Z66" s="9"/>
       <c r="AA66" s="9"/>
       <c r="AB66" s="8"/>
-      <c r="AD66" s="48"/>
-      <c r="AE66" s="48"/>
-      <c r="AF66" s="48"/>
-      <c r="AG66" s="48"/>
-      <c r="AH66" s="48"/>
-      <c r="AI66" s="48"/>
-      <c r="AJ66" s="48"/>
-      <c r="AK66" s="48"/>
-    </row>
-    <row r="67" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>4</v>
       </c>
@@ -4042,16 +3732,8 @@
       <c r="Z67" s="9"/>
       <c r="AA67" s="9"/>
       <c r="AB67" s="8"/>
-      <c r="AD67" s="48"/>
-      <c r="AE67" s="48"/>
-      <c r="AF67" s="48"/>
-      <c r="AG67" s="48"/>
-      <c r="AH67" s="48"/>
-      <c r="AI67" s="48"/>
-      <c r="AJ67" s="48"/>
-      <c r="AK67" s="48"/>
-    </row>
-    <row r="68" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>5</v>
       </c>
@@ -4083,16 +3765,8 @@
       <c r="Z68" s="9"/>
       <c r="AA68" s="9"/>
       <c r="AB68" s="8"/>
-      <c r="AD68" s="48"/>
-      <c r="AE68" s="48"/>
-      <c r="AF68" s="48"/>
-      <c r="AG68" s="48"/>
-      <c r="AH68" s="48"/>
-      <c r="AI68" s="48"/>
-      <c r="AJ68" s="48"/>
-      <c r="AK68" s="48"/>
-    </row>
-    <row r="69" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D69" t="s">
         <v>22</v>
       </c>
@@ -4120,16 +3794,8 @@
       <c r="Z69" s="9"/>
       <c r="AA69" s="9"/>
       <c r="AB69" s="8"/>
-      <c r="AD69" s="48"/>
-      <c r="AE69" s="48"/>
-      <c r="AF69" s="48"/>
-      <c r="AG69" s="48"/>
-      <c r="AH69" s="48"/>
-      <c r="AI69" s="48"/>
-      <c r="AJ69" s="48"/>
-      <c r="AK69" s="48"/>
-    </row>
-    <row r="70" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D70" t="s">
         <v>23</v>
       </c>
@@ -4157,16 +3823,8 @@
       <c r="Z70" s="9"/>
       <c r="AA70" s="9"/>
       <c r="AB70" s="8"/>
-      <c r="AD70" s="48"/>
-      <c r="AE70" s="48"/>
-      <c r="AF70" s="48"/>
-      <c r="AG70" s="48"/>
-      <c r="AH70" s="48"/>
-      <c r="AI70" s="48"/>
-      <c r="AJ70" s="48"/>
-      <c r="AK70" s="48"/>
-    </row>
-    <row r="71" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D71" t="s">
         <v>24</v>
       </c>
@@ -4194,16 +3852,8 @@
       <c r="Z71" s="9"/>
       <c r="AA71" s="9"/>
       <c r="AB71" s="8"/>
-      <c r="AD71" s="48"/>
-      <c r="AE71" s="48"/>
-      <c r="AF71" s="48"/>
-      <c r="AG71" s="48"/>
-      <c r="AH71" s="48"/>
-      <c r="AI71" s="48"/>
-      <c r="AJ71" s="48"/>
-      <c r="AK71" s="48"/>
-    </row>
-    <row r="72" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D72" t="s">
         <v>25</v>
       </c>
@@ -4231,16 +3881,8 @@
       <c r="Z72" s="9"/>
       <c r="AA72" s="9"/>
       <c r="AB72" s="8"/>
-      <c r="AD72" s="48"/>
-      <c r="AE72" s="48"/>
-      <c r="AF72" s="48"/>
-      <c r="AG72" s="48"/>
-      <c r="AH72" s="48"/>
-      <c r="AI72" s="48"/>
-      <c r="AJ72" s="48"/>
-      <c r="AK72" s="48"/>
-    </row>
-    <row r="73" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D73" t="s">
         <v>26</v>
       </c>
@@ -4268,16 +3910,8 @@
       <c r="Z73" s="9"/>
       <c r="AA73" s="9"/>
       <c r="AB73" s="8"/>
-      <c r="AD73" s="48"/>
-      <c r="AE73" s="48"/>
-      <c r="AF73" s="48"/>
-      <c r="AG73" s="48"/>
-      <c r="AH73" s="48"/>
-      <c r="AI73" s="48"/>
-      <c r="AJ73" s="48"/>
-      <c r="AK73" s="48"/>
-    </row>
-    <row r="74" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D74" t="s">
         <v>27</v>
       </c>
@@ -4305,16 +3939,8 @@
       <c r="Z74" s="9"/>
       <c r="AA74" s="9"/>
       <c r="AB74" s="8"/>
-      <c r="AD74" s="48"/>
-      <c r="AE74" s="48"/>
-      <c r="AF74" s="48"/>
-      <c r="AG74" s="48"/>
-      <c r="AH74" s="48"/>
-      <c r="AI74" s="48"/>
-      <c r="AJ74" s="48"/>
-      <c r="AK74" s="48"/>
-    </row>
-    <row r="75" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D75" t="s">
         <v>28</v>
       </c>
@@ -4342,16 +3968,8 @@
       <c r="Z75" s="17"/>
       <c r="AA75" s="17"/>
       <c r="AB75" s="18"/>
-      <c r="AD75" s="48"/>
-      <c r="AE75" s="48"/>
-      <c r="AF75" s="48"/>
-      <c r="AG75" s="48"/>
-      <c r="AH75" s="48"/>
-      <c r="AI75" s="48"/>
-      <c r="AJ75" s="48"/>
-      <c r="AK75" s="48"/>
-    </row>
-    <row r="76" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="D76" s="3"/>
@@ -4379,87 +3997,9 @@
       <c r="Z76" s="3"/>
       <c r="AA76" s="3"/>
       <c r="AB76" s="3"/>
-      <c r="AD76" s="48"/>
-      <c r="AE76" s="48"/>
-      <c r="AF76" s="48"/>
-      <c r="AG76" s="48"/>
-      <c r="AH76" s="48"/>
-      <c r="AI76" s="48"/>
-      <c r="AJ76" s="48"/>
-      <c r="AK76" s="48"/>
-    </row>
-    <row r="77" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="AD77" s="48"/>
-      <c r="AE77" s="48"/>
-      <c r="AF77" s="48"/>
-      <c r="AG77" s="48"/>
-      <c r="AH77" s="48"/>
-      <c r="AI77" s="48"/>
-      <c r="AJ77" s="48"/>
-      <c r="AK77" s="48"/>
-    </row>
-    <row r="78" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="AD78" s="48"/>
-      <c r="AE78" s="48"/>
-      <c r="AF78" s="48"/>
-      <c r="AG78" s="48"/>
-      <c r="AH78" s="48"/>
-      <c r="AI78" s="48"/>
-      <c r="AJ78" s="48"/>
-      <c r="AK78" s="48"/>
-    </row>
-    <row r="79" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="AD79" s="48"/>
-      <c r="AE79" s="48"/>
-      <c r="AF79" s="48"/>
-      <c r="AG79" s="48"/>
-      <c r="AH79" s="48"/>
-      <c r="AI79" s="48"/>
-      <c r="AJ79" s="48"/>
-      <c r="AK79" s="48"/>
-    </row>
-    <row r="80" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="AD80" s="48"/>
-      <c r="AE80" s="48"/>
-      <c r="AF80" s="48"/>
-      <c r="AG80" s="48"/>
-      <c r="AH80" s="48"/>
-      <c r="AI80" s="48"/>
-      <c r="AJ80" s="48"/>
-      <c r="AK80" s="48"/>
-    </row>
-    <row r="81" spans="30:37" x14ac:dyDescent="0.2">
-      <c r="AD81" s="48"/>
-      <c r="AE81" s="48"/>
-      <c r="AF81" s="48"/>
-      <c r="AG81" s="48"/>
-      <c r="AH81" s="48"/>
-      <c r="AI81" s="48"/>
-      <c r="AJ81" s="48"/>
-      <c r="AK81" s="48"/>
-    </row>
-    <row r="82" spans="30:37" x14ac:dyDescent="0.2">
-      <c r="AD82" s="48"/>
-      <c r="AE82" s="48"/>
-      <c r="AF82" s="48"/>
-      <c r="AG82" s="48"/>
-      <c r="AH82" s="48"/>
-      <c r="AI82" s="48"/>
-      <c r="AJ82" s="48"/>
-      <c r="AK82" s="48"/>
-    </row>
-    <row r="83" spans="30:37" x14ac:dyDescent="0.2">
-      <c r="AD83" s="48"/>
-      <c r="AE83" s="48"/>
-      <c r="AF83" s="48"/>
-      <c r="AG83" s="48"/>
-      <c r="AH83" s="48"/>
-      <c r="AI83" s="48"/>
-      <c r="AJ83" s="48"/>
-      <c r="AK83" s="48"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <mergeCells count="6">
     <mergeCell ref="AU3:AV14"/>
     <mergeCell ref="AI10:AI11"/>
@@ -4490,6 +4030,19 @@
   <dimension ref="A1:S51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="30.83203125" customWidth="1"/>
     <col min="19" max="19" width="19.6640625" customWidth="1"/>
     <col min="20" max="20" width="22.83203125" customWidth="1"/>
@@ -4571,7 +4124,7 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
       <c r="K2" s="7"/>
-      <c r="L2" s="43" t="str">
+      <c r="L2" s="38" t="str">
         <f>IF(LEN(User!AG2)=0,"",User!AG2)</f>
         <v/>
       </c>
@@ -4607,7 +4160,7 @@
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="7"/>
-      <c r="L3" s="43" t="str">
+      <c r="L3" s="38" t="str">
         <f>IF(LEN(User!AG3)=0,"",User!AG3)</f>
         <v/>
       </c>
@@ -4640,7 +4193,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="7"/>
-      <c r="L4" s="43" t="str">
+      <c r="L4" s="38" t="str">
         <f>IF(LEN(User!AG4)=0,"",User!AG4)</f>
         <v/>
       </c>
@@ -4672,7 +4225,7 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="7"/>
-      <c r="L5" s="43" t="str">
+      <c r="L5" s="38" t="str">
         <f>IF(LEN(User!AG5)=0,"",User!AG5)</f>
         <v/>
       </c>
@@ -4708,7 +4261,7 @@
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
       <c r="K6" s="7"/>
-      <c r="L6" s="43" t="str">
+      <c r="L6" s="38" t="str">
         <f>IF(LEN(User!AG6)=0,"",User!AG6)</f>
         <v/>
       </c>
@@ -4717,10 +4270,10 @@
       <c r="O6" s="7"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
-      <c r="R6" s="40" t="s">
+      <c r="R6" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="S6" s="41"/>
+      <c r="S6" s="52"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
@@ -4742,7 +4295,7 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="43" t="str">
+      <c r="L7" s="38" t="str">
         <f>IF(LEN(User!AG7)=0,"",User!AG7)</f>
         <v/>
       </c>
@@ -4772,7 +4325,7 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="43" t="str">
+      <c r="L8" s="38" t="str">
         <f>IF(LEN(User!AG8)=0,"",User!AG8)</f>
         <v/>
       </c>
@@ -4806,7 +4359,7 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="43" t="str">
+      <c r="L9" s="38" t="str">
         <f>IF(LEN(User!AG9)=0,"",User!AG9)</f>
         <v/>
       </c>
@@ -4840,7 +4393,7 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
       <c r="K10" s="7"/>
-      <c r="L10" s="43" t="str">
+      <c r="L10" s="38" t="str">
         <f>IF(LEN(User!AG10)=0,"",User!AG10)</f>
         <v/>
       </c>
@@ -4849,10 +4402,10 @@
       <c r="O10" s="7"/>
       <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
-      <c r="R10" s="38" t="s">
+      <c r="R10" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="S10" s="39"/>
+      <c r="S10" s="50"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
@@ -4874,7 +4427,7 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
       <c r="K11" s="7"/>
-      <c r="L11" s="43" t="str">
+      <c r="L11" s="38" t="str">
         <f>IF(LEN(User!AG11)=0,"",User!AG11)</f>
         <v/>
       </c>
@@ -4904,7 +4457,7 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
       <c r="K12" s="7"/>
-      <c r="L12" s="43" t="str">
+      <c r="L12" s="38" t="str">
         <f>IF(LEN(User!AG12)=0,"",User!AG12)</f>
         <v/>
       </c>
@@ -4940,7 +4493,7 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
       <c r="K13" s="7"/>
-      <c r="L13" s="43" t="str">
+      <c r="L13" s="38" t="str">
         <f>IF(LEN(User!AG13)=0,"",User!AG13)</f>
         <v/>
       </c>
@@ -4949,10 +4502,10 @@
       <c r="O13" s="7"/>
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
-      <c r="R13" s="38" t="s">
+      <c r="R13" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="S13" s="39"/>
+      <c r="S13" s="50"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="11">
@@ -4974,7 +4527,7 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
       <c r="K14" s="7"/>
-      <c r="L14" s="43" t="str">
+      <c r="L14" s="38" t="str">
         <f>IF(LEN(User!AG14)=0,"",User!AG14)</f>
         <v/>
       </c>
@@ -5010,7 +4563,7 @@
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
       <c r="K15" s="7"/>
-      <c r="L15" s="43" t="str">
+      <c r="L15" s="38" t="str">
         <f>IF(LEN(User!AG15)=0,"",User!AG15)</f>
         <v/>
       </c>
@@ -5044,7 +4597,7 @@
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
       <c r="K16" s="7"/>
-      <c r="L16" s="43" t="str">
+      <c r="L16" s="38" t="str">
         <f>IF(LEN(User!AG16)=0,"",User!AG16)</f>
         <v/>
       </c>
@@ -5078,7 +4631,7 @@
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
       <c r="K17" s="7"/>
-      <c r="L17" s="43" t="str">
+      <c r="L17" s="38" t="str">
         <f>IF(LEN(User!AG17)=0,"",User!AG17)</f>
         <v/>
       </c>
@@ -5087,10 +4640,10 @@
       <c r="O17" s="7"/>
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
-      <c r="R17" s="58" t="s">
+      <c r="R17" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="S17" s="41"/>
+      <c r="S17" s="52"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="11">
@@ -5112,7 +4665,7 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
       <c r="K18" s="7"/>
-      <c r="L18" s="43" t="str">
+      <c r="L18" s="38" t="str">
         <f>IF(LEN(User!AG18)=0,"",User!AG18)</f>
         <v/>
       </c>
@@ -5142,7 +4695,7 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
       <c r="K19" s="7"/>
-      <c r="L19" s="43" t="str">
+      <c r="L19" s="38" t="str">
         <f>IF(LEN(User!AG19)=0,"",User!AG19)</f>
         <v/>
       </c>
@@ -5172,7 +4725,7 @@
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
       <c r="K20" s="7"/>
-      <c r="L20" s="43" t="str">
+      <c r="L20" s="38" t="str">
         <f>IF(LEN(User!AG20)=0,"",User!AG20)</f>
         <v/>
       </c>
@@ -5202,7 +4755,7 @@
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
       <c r="K21" s="7"/>
-      <c r="L21" s="43" t="str">
+      <c r="L21" s="38" t="str">
         <f>IF(LEN(User!AG21)=0,"",User!AG21)</f>
         <v/>
       </c>
@@ -5232,7 +4785,7 @@
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
       <c r="K22" s="7"/>
-      <c r="L22" s="43" t="str">
+      <c r="L22" s="38" t="str">
         <f>IF(LEN(User!AG22)=0,"",User!AG22)</f>
         <v/>
       </c>
@@ -5262,7 +4815,7 @@
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
       <c r="K23" s="7"/>
-      <c r="L23" s="43" t="str">
+      <c r="L23" s="38" t="str">
         <f>IF(LEN(User!AG23)=0,"",User!AG23)</f>
         <v/>
       </c>
@@ -5292,7 +4845,7 @@
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
       <c r="K24" s="7"/>
-      <c r="L24" s="43" t="str">
+      <c r="L24" s="38" t="str">
         <f>IF(LEN(User!AG24)=0,"",User!AG24)</f>
         <v/>
       </c>
@@ -5322,7 +4875,7 @@
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
       <c r="K25" s="7"/>
-      <c r="L25" s="43" t="str">
+      <c r="L25" s="38" t="str">
         <f>IF(LEN(User!AG25)=0,"",User!AG25)</f>
         <v/>
       </c>
@@ -5352,7 +4905,7 @@
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
       <c r="K26" s="7"/>
-      <c r="L26" s="43" t="str">
+      <c r="L26" s="38" t="str">
         <f>IF(LEN(User!AG26)=0,"",User!AG26)</f>
         <v/>
       </c>
@@ -5382,7 +4935,7 @@
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
       <c r="K27" s="7"/>
-      <c r="L27" s="43" t="str">
+      <c r="L27" s="38" t="str">
         <f>IF(LEN(User!AG27)=0,"",User!AG27)</f>
         <v/>
       </c>
@@ -5412,7 +4965,7 @@
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
       <c r="K28" s="7"/>
-      <c r="L28" s="43" t="str">
+      <c r="L28" s="38" t="str">
         <f>IF(LEN(User!AG28)=0,"",User!AG28)</f>
         <v/>
       </c>
@@ -5442,7 +4995,7 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
       <c r="K29" s="7"/>
-      <c r="L29" s="43" t="str">
+      <c r="L29" s="38" t="str">
         <f>IF(LEN(User!AG29)=0,"",User!AG29)</f>
         <v/>
       </c>
@@ -5472,7 +5025,7 @@
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
       <c r="K30" s="7"/>
-      <c r="L30" s="43" t="str">
+      <c r="L30" s="38" t="str">
         <f>IF(LEN(User!AG30)=0,"",User!AG30)</f>
         <v/>
       </c>
@@ -5502,7 +5055,7 @@
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
       <c r="K31" s="7"/>
-      <c r="L31" s="43" t="str">
+      <c r="L31" s="38" t="str">
         <f>IF(LEN(User!AG31)=0,"",User!AG31)</f>
         <v/>
       </c>
@@ -5532,7 +5085,7 @@
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
       <c r="K32" s="7"/>
-      <c r="L32" s="43" t="str">
+      <c r="L32" s="38" t="str">
         <f>IF(LEN(User!AG32)=0,"",User!AG32)</f>
         <v/>
       </c>
@@ -5562,7 +5115,7 @@
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
       <c r="K33" s="7"/>
-      <c r="L33" s="43" t="str">
+      <c r="L33" s="38" t="str">
         <f>IF(LEN(User!AG33)=0,"",User!AG33)</f>
         <v/>
       </c>
@@ -5592,7 +5145,7 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
       <c r="K34" s="7"/>
-      <c r="L34" s="43" t="str">
+      <c r="L34" s="38" t="str">
         <f>IF(LEN(User!AG34)=0,"",User!AG34)</f>
         <v/>
       </c>
@@ -5622,7 +5175,7 @@
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
       <c r="K35" s="7"/>
-      <c r="L35" s="43" t="str">
+      <c r="L35" s="38" t="str">
         <f>IF(LEN(User!AG35)=0,"",User!AG35)</f>
         <v/>
       </c>
@@ -5652,7 +5205,7 @@
       <c r="I36" s="6"/>
       <c r="J36" s="6"/>
       <c r="K36" s="7"/>
-      <c r="L36" s="43" t="str">
+      <c r="L36" s="38" t="str">
         <f>IF(LEN(User!AG36)=0,"",User!AG36)</f>
         <v/>
       </c>
@@ -5682,7 +5235,7 @@
       <c r="I37" s="6"/>
       <c r="J37" s="6"/>
       <c r="K37" s="7"/>
-      <c r="L37" s="43" t="str">
+      <c r="L37" s="38" t="str">
         <f>IF(LEN(User!AG37)=0,"",User!AG37)</f>
         <v/>
       </c>
@@ -5712,7 +5265,7 @@
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
       <c r="K38" s="7"/>
-      <c r="L38" s="43" t="str">
+      <c r="L38" s="38" t="str">
         <f>IF(LEN(User!AG38)=0,"",User!AG38)</f>
         <v/>
       </c>
@@ -5742,7 +5295,7 @@
       <c r="I39" s="6"/>
       <c r="J39" s="6"/>
       <c r="K39" s="7"/>
-      <c r="L39" s="43" t="str">
+      <c r="L39" s="38" t="str">
         <f>IF(LEN(User!AG39)=0,"",User!AG39)</f>
         <v/>
       </c>
@@ -5772,7 +5325,7 @@
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
       <c r="K40" s="7"/>
-      <c r="L40" s="43" t="str">
+      <c r="L40" s="38" t="str">
         <f>IF(LEN(User!AG40)=0,"",User!AG40)</f>
         <v/>
       </c>
@@ -5802,7 +5355,7 @@
       <c r="I41" s="6"/>
       <c r="J41" s="6"/>
       <c r="K41" s="7"/>
-      <c r="L41" s="43" t="str">
+      <c r="L41" s="38" t="str">
         <f>IF(LEN(User!AG41)=0,"",User!AG41)</f>
         <v/>
       </c>
@@ -5832,7 +5385,7 @@
       <c r="I42" s="6"/>
       <c r="J42" s="6"/>
       <c r="K42" s="7"/>
-      <c r="L42" s="43" t="str">
+      <c r="L42" s="38" t="str">
         <f>IF(LEN(User!AG42)=0,"",User!AG42)</f>
         <v/>
       </c>
@@ -5862,7 +5415,7 @@
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
       <c r="K43" s="7"/>
-      <c r="L43" s="43" t="str">
+      <c r="L43" s="38" t="str">
         <f>IF(LEN(User!AG43)=0,"",User!AG43)</f>
         <v/>
       </c>
@@ -5892,7 +5445,7 @@
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
       <c r="K44" s="7"/>
-      <c r="L44" s="43" t="str">
+      <c r="L44" s="38" t="str">
         <f>IF(LEN(User!AG44)=0,"",User!AG44)</f>
         <v/>
       </c>
@@ -5922,7 +5475,7 @@
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
       <c r="K45" s="7"/>
-      <c r="L45" s="43" t="str">
+      <c r="L45" s="38" t="str">
         <f>IF(LEN(User!AG45)=0,"",User!AG45)</f>
         <v/>
       </c>
@@ -5952,7 +5505,7 @@
       <c r="I46" s="6"/>
       <c r="J46" s="6"/>
       <c r="K46" s="7"/>
-      <c r="L46" s="43" t="str">
+      <c r="L46" s="38" t="str">
         <f>IF(LEN(User!AG46)=0,"",User!AG46)</f>
         <v/>
       </c>
@@ -5982,7 +5535,7 @@
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
       <c r="K47" s="7"/>
-      <c r="L47" s="43" t="str">
+      <c r="L47" s="38" t="str">
         <f>IF(LEN(User!AG47)=0,"",User!AG47)</f>
         <v/>
       </c>
@@ -6004,7 +5557,7 @@
         <f>IF(LEN(User!AF48)=0,"",User!AF48)</f>
         <v/>
       </c>
-      <c r="D48" s="44"/>
+      <c r="D48" s="39"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="6"/>
@@ -6012,7 +5565,7 @@
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
       <c r="K48" s="7"/>
-      <c r="L48" s="43" t="str">
+      <c r="L48" s="38" t="str">
         <f>IF(LEN(User!AG48)=0,"",User!AG48)</f>
         <v/>
       </c>
@@ -6034,7 +5587,7 @@
         <f>IF(LEN(User!AF49)=0,"",User!AF49)</f>
         <v/>
       </c>
-      <c r="D49" s="44"/>
+      <c r="D49" s="39"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
       <c r="G49" s="6"/>
@@ -6042,7 +5595,7 @@
       <c r="I49" s="6"/>
       <c r="J49" s="6"/>
       <c r="K49" s="7"/>
-      <c r="L49" s="43" t="str">
+      <c r="L49" s="38" t="str">
         <f>IF(LEN(User!AG49)=0,"",User!AG49)</f>
         <v/>
       </c>
@@ -6064,7 +5617,7 @@
         <f>IF(LEN(User!AF50)=0,"",User!AF50)</f>
         <v/>
       </c>
-      <c r="D50" s="44"/>
+      <c r="D50" s="39"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
       <c r="G50" s="6"/>
@@ -6072,7 +5625,7 @@
       <c r="I50" s="6"/>
       <c r="J50" s="6"/>
       <c r="K50" s="7"/>
-      <c r="L50" s="43" t="str">
+      <c r="L50" s="38" t="str">
         <f>IF(LEN(User!AG50)=0,"",User!AG50)</f>
         <v/>
       </c>
@@ -6102,7 +5655,7 @@
       <c r="I51" s="12"/>
       <c r="J51" s="12"/>
       <c r="K51" s="16"/>
-      <c r="L51" s="57"/>
+      <c r="L51" s="41"/>
       <c r="M51" s="16"/>
       <c r="N51" s="16"/>
       <c r="O51" s="16"/>
@@ -6110,7 +5663,7 @@
       <c r="Q51" s="12"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <mergeCells count="4">
     <mergeCell ref="R13:S13"/>
     <mergeCell ref="R6:S6"/>
